--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332E93A7-46A4-4453-9740-6F368B3D74F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE80BCD-1B0F-4B4C-9E56-AE947E30D1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="57">
   <si>
     <t>itemId</t>
   </si>
@@ -149,10 +149,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>보급형 신발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>healthFlat</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -225,6 +221,14 @@
   </si>
   <si>
     <t>UniqueEffect_QuantumShoes</t>
+  </si>
+  <si>
+    <t>닌자의 움직임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -302,13 +306,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -620,7 +623,7 @@
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.8984375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14.8984375" style="4" customWidth="1"/>
     <col min="2" max="3" width="18.296875" customWidth="1"/>
     <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.69921875" customWidth="1"/>
@@ -632,96 +635,96 @@
     <col min="13" max="13" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="J1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="J2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>1001</v>
       </c>
       <c r="B3" t="s">
@@ -737,7 +740,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3">
         <v>50</v>
@@ -756,7 +759,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>2001</v>
       </c>
       <c r="B4" t="s">
@@ -791,11 +794,11 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>3001</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>35</v>
@@ -804,16 +807,16 @@
         <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>1.2</v>
       </c>
       <c r="K5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -826,11 +829,11 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>3002</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -839,19 +842,19 @@
         <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>1.5</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -864,7 +867,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="7"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -874,7 +877,7 @@
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12" s="7"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -913,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
         <v>50</v>
-      </c>
-      <c r="D1" t="s">
-        <v>51</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -940,7 +943,7 @@
         <v>27</v>
       </c>
       <c r="K1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s">
         <v>1</v>
@@ -1013,7 +1016,7 @@
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1045,13 +1048,13 @@
         <v>4501</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -1066,7 +1069,7 @@
         <v>20</v>
       </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -1123,16 +1126,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
@@ -1181,16 +1184,16 @@
         <v>5001</v>
       </c>
       <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
         <v>46</v>
-      </c>
-      <c r="C3" t="s">
-        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>1</v>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -644,7 +644,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>01000001</t>
+          <t>item.weapon.greatsword.basic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>01000002</t>
+          <t>item.weapon.shotgun.flamethrower</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -948,7 +948,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>01010001</t>
+          <t>item.armor.helmet.basic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>01020001</t>
+          <t>item.armor.chest.sturdy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>01030001</t>
+          <t>item.armor.boots.ninja_movement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>01030002</t>
+          <t>item.armor.boots.quantum_shoes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>01040001</t>
+          <t>item.potion.red</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3453506-0D76-47B5-BCBF-24EB2BD4BAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3030D6DA-7D5F-46E3-8B7B-612061D0AA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="83">
   <si>
     <t>itemId</t>
   </si>
@@ -249,6 +249,50 @@
   </si>
   <si>
     <t>보통의 코어보다 출력이 높은 코어입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나뭇가지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fighter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계 파괴자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blunt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.treebranch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.mechanicaldestroyer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단단한 기계들을 무자비하게 파괴할 수 있는 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길거리에 굴러다닐 법한 나뭇가지입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -646,16 +690,17 @@
   <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.8984375" customWidth="1"/>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.296875" customWidth="1"/>
     <col min="4" max="4" width="12.69921875" customWidth="1"/>
+    <col min="5" max="5" width="9.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.69921875" customWidth="1"/>
     <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="15.3984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.09765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" customWidth="1"/>
-    <col min="12" max="12" width="39.09765625" customWidth="1"/>
+    <col min="12" max="12" width="50" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -828,6 +873,82 @@
       </c>
       <c r="O4">
         <v>1300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>70</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" t="s">
+        <v>80</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3030D6DA-7D5F-46E3-8B7B-612061D0AA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB52584-098A-432A-9D51-6620D074D12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="113">
   <si>
     <t>itemId</t>
   </si>
@@ -293,6 +293,119 @@
   </si>
   <si>
     <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.noentrysign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진입 금지 표지판</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Advanced</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.axe.icecrusher</t>
+  </si>
+  <si>
+    <t>아이스 크러셔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Axe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.axe.inferno</t>
+  </si>
+  <si>
+    <t>인페르노</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강력한 냉기를 품은 도끼입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 도끼가 품은 화염은 적에게 지옥을 선사합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.baseballbat</t>
+  </si>
+  <si>
+    <t>item.weapon.blunt.lightsaber</t>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.crusader</t>
+  </si>
+  <si>
+    <t>히히 못가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.guardiansjustice</t>
+  </si>
+  <si>
+    <t>크루세이더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수호자의 정의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatSword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠따</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라이트세이버</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.ironpipe</t>
+  </si>
+  <si>
+    <t>쇠 파이프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야구 빠따를 전투용으로 개조했습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광선검입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성스러운 일격을 날릴 수 있는 대검입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정의는 승리한다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고철 처리장에서 가져온 녹 슨 파이프입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
@@ -819,7 +932,7 @@
         <v>26</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
         <v>27</v>
@@ -951,25 +1064,309 @@
         <v>100</v>
       </c>
     </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s">
+        <v>99</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8">
+        <v>35</v>
+      </c>
+      <c r="J8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="J9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" t="s">
+        <v>108</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10">
+        <v>300</v>
+      </c>
+    </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>35</v>
+      </c>
+      <c r="J11" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>3</v>
+      </c>
+      <c r="O11">
+        <v>1000</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12">
+        <v>65</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2</v>
+      </c>
+      <c r="N12" s="1">
+        <v>3</v>
+      </c>
+      <c r="O12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>40</v>
+      </c>
+      <c r="J13" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" t="s">
+        <v>111</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14">
+        <v>300</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A62EA5-FF37-4152-A392-5DB7C16E3514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90287463-6C29-4600-9EFE-6179124C40D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1968" yWindow="1440" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="154">
   <si>
     <t>itemId</t>
   </si>
@@ -475,6 +475,30 @@
   </si>
   <si>
     <t>데브리스-9의 결정체가 응축된 전설 무기입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐열 절단 대검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatSword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대한 칼날은 폐열을 가장자리에 집중시켜 견고한 기계도 절단할 수 있게 해줍니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.wasteheatcleaver</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1535,7 +1559,42 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A19" s="12"/>
+      <c r="A19" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19">
+        <v>45</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="M19" s="9">
+        <v>2</v>
+      </c>
+      <c r="N19" s="9">
+        <v>3</v>
+      </c>
+      <c r="O19" s="9">
+        <v>6000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90287463-6C29-4600-9EFE-6179124C40D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDCB322-C258-4E85-9877-8C2F054FB16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1968" yWindow="1440" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="194">
   <si>
     <t>itemId</t>
   </si>
@@ -499,6 +499,158 @@
   </si>
   <si>
     <t>item.weapon.greatsword.wasteheatcleaver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.axe.wildfire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와일드파이어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.thighbone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.superrefrigerant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초냉매</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.morningstar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침의 별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.magicstaff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법(물리) 지팡이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.nightsword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밤의 칼날</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.rusty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹슨 대검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blunt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우주 괴물 대퇴골</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Advanced</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꺼지지 않는 불씨를 품은 도끼입니다. 휘두를 때마다 잠들어 있던 열기가 다시 타오릅니다.</t>
+  </si>
+  <si>
+    <t>정체불명의 우주 괴물에게서 나온 대퇴골입니다. 뼈라고 믿기 어려울 만큼 무겁고 단단합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>극저온의 냉매가 봉인되어 있습니다. 충격을 받을 때마다 주변의 열을 무자비하게 빼앗습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새벽하늘에서 가장 밝게 빛나는 별의 이름을 가진 무기입니다. 맞은 사람도 잠시 별을 볼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>마력이 없어도 사용할 수 있는 마법 지팡이입니다. 주문은 간단합니다. 힘껏 휘두르세요.</t>
+  </si>
+  <si>
+    <t>빛을 삼킨 듯 검게 물든 대검입니다. 어둠 속에서는 칼날의 경계조차 흐릿해집니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹이 슬고 날도 무뎌진 낡은 대검입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.armor.boots.discardedboostermodule</t>
+  </si>
+  <si>
+    <t>폐기된 부스터 모듈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐기된 기동 로봇에서 떼어낸 부스터 모듈입니다. 안전 기준은 충족하지 못했지만, 속도 기준은 확실히 충족합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.armor.helmet.signaljammer</t>
+  </si>
+  <si>
+    <t>군집 신호 교란기</t>
+  </si>
+  <si>
+    <t>item.armor.chest.solargrace</t>
+  </si>
+  <si>
+    <t>태양의 은혜</t>
+  </si>
+  <si>
+    <t>Helmet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변의 군집 통신 신호에 잡음을 섞어 넣는 장치입니다. 적들은 혼란스러워지고, 착용자는 머리가 조금 아파집니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양 에너지를 흡수해 착용자를 보호하는 갑옷입니다. 별 하나가 보내는 은혜치고는 꽤나 뜨겁습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -580,7 +732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -604,6 +756,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -837,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -1596,6 +1752,275 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A20" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G20">
+        <v>45</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="M20" s="9">
+        <v>2</v>
+      </c>
+      <c r="N20" s="9">
+        <v>3</v>
+      </c>
+      <c r="O20" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21">
+        <v>25</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="M21" s="9">
+        <v>2</v>
+      </c>
+      <c r="N21" s="9">
+        <v>3</v>
+      </c>
+      <c r="O21" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A22" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="M22" s="9">
+        <v>2</v>
+      </c>
+      <c r="N22" s="9">
+        <v>3</v>
+      </c>
+      <c r="O22" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23">
+        <v>40</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="M23" s="9">
+        <v>1</v>
+      </c>
+      <c r="N23" s="9">
+        <v>3</v>
+      </c>
+      <c r="O23" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24">
+        <v>35</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="M24" s="9">
+        <v>1</v>
+      </c>
+      <c r="N24" s="9">
+        <v>3</v>
+      </c>
+      <c r="O24" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A25" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25">
+        <v>35</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="M25" s="9">
+        <v>2</v>
+      </c>
+      <c r="N25" s="9">
+        <v>3</v>
+      </c>
+      <c r="O25" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A26" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="M26" s="9">
+        <v>2</v>
+      </c>
+      <c r="N26" s="9">
+        <v>4</v>
+      </c>
+      <c r="O26" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C28" s="12"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1607,7 +2032,7 @@
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="32.09765625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="38.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.296875" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
     <col min="5" max="5" width="9.8984375" customWidth="1"/>
@@ -1615,7 +2040,7 @@
     <col min="7" max="7" width="14.09765625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="10" width="22.5" customWidth="1"/>
-    <col min="11" max="11" width="39.09765625" customWidth="1"/>
+    <col min="11" max="11" width="100.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.296875" customWidth="1"/>
     <col min="13" max="13" width="12.19921875" customWidth="1"/>
   </cols>
@@ -1734,10 +2159,10 @@
         <v>78</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
         <v>40</v>
@@ -1798,7 +2223,7 @@
         <v>86</v>
       </c>
       <c r="G5">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="s">
         <v>87</v>
@@ -1833,7 +2258,7 @@
         <v>86</v>
       </c>
       <c r="G6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J6" t="s">
         <v>90</v>
@@ -1849,6 +2274,111 @@
       </c>
       <c r="N6">
         <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7">
+        <v>1.3</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8">
+        <v>120</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>10000</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
@@ -2150,10 +2680,10 @@
         <v>108</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>3000</v>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDCB322-C258-4E85-9877-8C2F054FB16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF488696-A9AA-439E-9CBF-20A29E1B4F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="209">
   <si>
     <t>itemId</t>
   </si>
@@ -652,6 +652,62 @@
   <si>
     <t>태양 에너지를 흡수해 착용자를 보호하는 갑옷입니다. 별 하나가 보내는 은혜치고는 꽤나 뜨겁습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공허의 수확자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체인소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아크 블레이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코어 브레이커</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강제 정비 도구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.axe.phaseharvester</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.arcblade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.corebreaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.greatsword.chainsaw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.weapon.blunt.shovel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공허 에너지를 칼날 형태로 압축한 전투용 낫입니다. 한 번 휘두를 때마다 보랏빛 궤적이 공간과 장갑을 함께 베어냅니다.</t>
+  </si>
+  <si>
+    <t>검신을 따라 고전압 전류를 순환시키는 전투용 도검입니다. 절단면으로 방전된 전류가 내부 회로까지 파고듭니다.</t>
+  </si>
+  <si>
+    <t>폐기 로봇의 장갑을 절단하기 위해 만들어진 산업용 공구입니다. 전쟁터에서는 굳이 폐기 판정을 기다릴 필요가 없다는 사실이 밝혀졌습니다.</t>
+  </si>
+  <si>
+    <t>중앙 동력핵의 출력을 검신 전체에 방출하는 대형 병기입니다. 외장갑을 부수는 것은 시작일 뿐, 진짜 목표는 그 안쪽의 동력 코어입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야전 정비반에서 사용하던 다목적 중장비입니다. 정상적인 정비 절차로 해결되지 않는 기계는 충분한 운동에너지를 가하면 대개 조용해집니다.</t>
   </si>
 </sst>
 </file>
@@ -732,7 +788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -759,7 +815,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -993,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
@@ -2018,8 +2073,195 @@
         <v>50</v>
       </c>
     </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A27" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27">
+        <v>65</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="M27" s="9">
+        <v>3</v>
+      </c>
+      <c r="N27" s="9">
+        <v>4</v>
+      </c>
+      <c r="O27" s="9">
+        <v>10000</v>
+      </c>
+    </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C28" s="12"/>
+      <c r="A28" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28">
+        <v>50</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="M28" s="9">
+        <v>2</v>
+      </c>
+      <c r="N28" s="9">
+        <v>3</v>
+      </c>
+      <c r="O28" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29">
+        <v>45</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M29" s="9">
+        <v>2</v>
+      </c>
+      <c r="N29" s="9">
+        <v>3</v>
+      </c>
+      <c r="O29" s="9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A30" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G30">
+        <v>30</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="M30" s="9">
+        <v>1</v>
+      </c>
+      <c r="N30" s="9">
+        <v>3</v>
+      </c>
+      <c r="O30" s="9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A31" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="M31" s="9">
+        <v>1</v>
+      </c>
+      <c r="N31" s="9">
+        <v>4</v>
+      </c>
+      <c r="O31" s="9">
+        <v>300</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2289,7 +2531,7 @@
       <c r="D7" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>170</v>
       </c>
       <c r="F7" t="s">
@@ -2324,7 +2566,7 @@
       <c r="D8" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>170</v>
       </c>
       <c r="F8" t="s">
@@ -2359,7 +2601,7 @@
       <c r="D9" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>144</v>
       </c>
       <c r="F9" t="s">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Project2\Assets\Resources\DataFiles\ItemData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DE5385-1C15-4259-899A-7B94519F46A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791C5D3D-CB9E-455A-BDC0-BCEF356FF8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3708" yWindow="3180" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponDefinitions" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="233">
   <si>
     <t>itemId</t>
   </si>
@@ -721,6 +721,47 @@
   <si>
     <t>전설적인 닌자의 움직임을 재현하도록 설계된 특수 전투화입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UE_MechanicalDestroyer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UE_HeartOfDebris</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고철 압축기</t>
+  </si>
+  <si>
+    <t>item.relic.scrapcompactor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UE_ScrapCompactor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파괴된 기계의 잔해를 압축해 재활용하는 장치입니다. 전장에는 원료가 넘쳐납니다.</t>
+  </si>
+  <si>
+    <t>item.relic.overclockcore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오버클럭 코어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UE_OverclockCore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전 한계를 무시하고 출력을 끌어올리는 개조 동력 코어입니다. 성능을 얻는 데에는 언제나 대가가 따릅니다.</t>
   </si>
 </sst>
 </file>
@@ -1280,6 +1321,9 @@
       <c r="J5" t="s">
         <v>35</v>
       </c>
+      <c r="K5" s="11" t="s">
+        <v>222</v>
+      </c>
       <c r="L5" t="s">
         <v>36</v>
       </c>
@@ -1776,6 +1820,9 @@
       </c>
       <c r="J18" s="11" t="s">
         <v>47</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>80</v>
@@ -3164,14 +3211,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
     <col min="2" max="2" width="11.09765625" customWidth="1"/>
     <col min="3" max="3" width="8.5" customWidth="1"/>
     <col min="5" max="5" width="21.09765625" customWidth="1"/>
-    <col min="6" max="6" width="40.09765625" customWidth="1"/>
+    <col min="6" max="6" width="96.09765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.796875" customWidth="1"/>
     <col min="8" max="8" width="10.3984375" customWidth="1"/>
     <col min="9" max="9" width="8.8984375" customWidth="1"/>
@@ -3284,10 +3331,10 @@
         <v>159</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
         <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
       </c>
       <c r="I4">
         <v>1200</v>
@@ -3320,6 +3367,64 @@
       </c>
       <c r="I5">
         <v>3000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>6000</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -5989,7 +5989,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">공장에서 찍어낸 기계장치의 코어입니다. </t>
+          <t>공장에서 찍어낸 기계장치의 코어입니다.</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R0705aaa1a80c4875"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Rb7a6ebcb388e4105"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rde7363b2d9a64383"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Re03ca71ce1494764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rbd4db736c95b4e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="Rcf545d2bcfb9463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Ra75f02ba18ef4eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R26dc2b522e1b49bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R69b52554b0d84327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rdfd612528b574a20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4002,6 +4002,393 @@
         <x:v>12000</x:v>
       </x:c>
     </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>item.weapon.rifle.smilesignal</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>스마일 시그널</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G61" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H61"/>
+      <x:c r="I61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K61"/>
+      <x:c r="L61" t="str">
+        <x:v>거너의 색과 얼굴 스티커를 담아 제작한 전용 에너지 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M61" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N61" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O61" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>item.weapon.rifle.dustsparrow</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>모래 참새</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F62" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G62" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H62"/>
+      <x:c r="I62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J62" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K62"/>
+      <x:c r="L62" t="str">
+        <x:v>모래 먼지 속에서도 안정적으로 작동하는 경량 일체형 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N62" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O62" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>item.weapon.grenadelauncher.pulsecask</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>펄스 챔버</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E63" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F63" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G63" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H63"/>
+      <x:c r="I63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J63" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K63"/>
+      <x:c r="L63" t="str">
+        <x:v>밀폐된 펄스 챔버로 에너지를 압축하는 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M63" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O63" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>item.weapon.rifle.glassrail</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>유리빛 궤도</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E64" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F64" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G64" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H64"/>
+      <x:c r="I64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J64" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K64"/>
+      <x:c r="L64" t="str">
+        <x:v>투명 덮개 속 단일 에너지 도관을 사용하는 정밀 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M64" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N64" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O64" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>item.weapon.shotgun.embercoil</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>잔불 고리</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E65" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F65" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G65" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H65"/>
+      <x:c r="I65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J65" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K65"/>
+      <x:c r="L65" t="str">
+        <x:v>열차폐판 안쪽의 잔불 코일을 순간적으로 방출하는 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M65" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O65" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>item.weapon.grenadelauncher.halomortar</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>헤일로 박격포</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G66" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H66"/>
+      <x:c r="I66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K66"/>
+      <x:c r="L66" t="str">
+        <x:v>밀폐된 환형 투사기로 탄도를 안정시키는 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M66" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N66" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O66" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>item.weapon.shotgun.echovault</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>에코 챔버</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G67" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H67"/>
+      <x:c r="I67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K67"/>
+      <x:c r="L67" t="str">
+        <x:v>직선형 공명실에 충격파를 축적하는 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M67" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N67" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O67" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>item.weapon.grenadelauncher.sunfallengine</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>일식 기관</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G68" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H68"/>
+      <x:c r="I68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J68" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K68"/>
+      <x:c r="L68" t="str">
+        <x:v>태양 코어의 열을 한 덩어리로 압축해 발사하는 중화기입니다.</x:v>
+      </x:c>
+      <x:c r="M68" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N68" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O68" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>item.weapon.shotgun.starforgebreach</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>스타 브리처</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H69"/>
+      <x:c r="I69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K69"/>
+      <x:c r="L69" t="str">
+        <x:v>제련 코어의 에너지를 넓은 총구로 방출하는 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M69" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N69" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O69" t="n">
+        <x:v>12000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="Rcf545d2bcfb9463d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Ra75f02ba18ef4eb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R26dc2b522e1b49bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R69b52554b0d84327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rdfd612528b574a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R9fdc427c09634b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R24ff8042327d4ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Raabc0a8f2da94690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R9c112b282a2044ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rad3d5126b6b14c78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4389,6 +4389,719 @@
         <x:v>12000</x:v>
       </x:c>
     </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>item.weapon.shotgun.voidbarrage</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>공허 연발포</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G70" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+      <x:c r="J70" t="str">
+        <x:v>Electric</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>UE_VoidBarrage</x:v>
+      </x:c>
+      <x:c r="L70" t="str">
+        <x:v>다중 공진 총구가 공허 전하를 한꺼번에 토해내는 중형 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M70" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N70" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O70" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>item.weapon.shotgun.redlinebreacher</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>레드라인 브리처</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E71" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F71" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G71" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
+      <x:c r="J71" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K71"/>
+      <x:c r="L71" t="str">
+        <x:v>주황색 충격 완충부와 수동 펌프를 갖춘 신뢰성 높은 제압용 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M71" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N71" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O71" t="n">
+        <x:v>600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>item.weapon.shotgun.goldentwinstar</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>황금 쌍성</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E72" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F72" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G72" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
+      <x:c r="J72" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K72" t="str">
+        <x:v>UE_GoldenTwinStar</x:v>
+      </x:c>
+      <x:c r="L72" t="str">
+        <x:v>황금 장갑 아래 두 개의 포신을 나란히 묶은 고출력 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M72" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N72" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O72" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>item.weapon.shotgun.magmacrusher</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>용암 파쇄포</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E73" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F73" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G73" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
+      <x:c r="J73" t="str">
+        <x:v>Fire</x:v>
+      </x:c>
+      <x:c r="K73" t="str">
+        <x:v>UE_MagmaCrusher</x:v>
+      </x:c>
+      <x:c r="L73" t="str">
+        <x:v>용융 열이 갈라진 외피 사이로 새어 나오는 근접 파쇄용 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M73" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N73" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O73" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>item.weapon.shotgun.whiterefrigerant</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>백색 냉매</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E74" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F74" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G74" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
+      <x:c r="J74" t="str">
+        <x:v>Ice</x:v>
+      </x:c>
+      <x:c r="K74"/>
+      <x:c r="L74" t="str">
+        <x:v>백색 외장과 냉각 앰풀로 반동열을 제어하는 경량 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M74" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N74" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O74" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>item.weapon.shotgun.thundercoil</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>뇌전 코일</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E75" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F75" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G75" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H75"/>
+      <x:c r="I75"/>
+      <x:c r="J75" t="str">
+        <x:v>Electric</x:v>
+      </x:c>
+      <x:c r="K75" t="str">
+        <x:v>UE_ThunderCoil</x:v>
+      </x:c>
+      <x:c r="L75" t="str">
+        <x:v>청색 코일에 전하를 축적해 산탄과 함께 방전하는 전자 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M75" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N75" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O75" t="n">
+        <x:v>6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>item.weapon.shotgun.scrapdrum</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>고철 탄통</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E76" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F76" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G76" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H76"/>
+      <x:c r="I76"/>
+      <x:c r="J76" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K76"/>
+      <x:c r="L76" t="str">
+        <x:v>폐공장 탄통과 배관을 이어 붙인 짧고 튼튼한 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M76" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O76" t="n">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>item.weapon.rifle.ioncascade</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>이온 폭포</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E77" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F77" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G77" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
+      <x:c r="J77" t="str">
+        <x:v>Electric</x:v>
+      </x:c>
+      <x:c r="K77" t="str">
+        <x:v>UE_IonCascade</x:v>
+      </x:c>
+      <x:c r="L77" t="str">
+        <x:v>백색 프레임의 대형 이온 코어를 연속 순환시키는 에너지 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M77" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N77" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O77" t="n">
+        <x:v>6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>item.weapon.rifle.nightwarden</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>야간 감시자</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E78" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F78" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G78" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
+      <x:c r="J78" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K78"/>
+      <x:c r="L78" t="str">
+        <x:v>빛을 억제한 녹색 외장과 소형 표적등을 갖춘 잠입용 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M78" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N78" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O78" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>item.weapon.rifle.workspark</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>공업 스파크</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E79" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F79" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G79" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
+      <x:c r="J79" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K79"/>
+      <x:c r="L79" t="str">
+        <x:v>건설 장비의 안전색과 고출력 모터를 재사용한 산업용 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M79" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N79" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O79" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>item.weapon.rifle.rusthound</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>녹슨 사냥개</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E80" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F80" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
+      <x:c r="J80" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K80"/>
+      <x:c r="L80" t="str">
+        <x:v>녹슨 부품과 노출 배선을 엮어 만든 집요한 생존형 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M80" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N80" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O80" t="n">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>item.weapon.rifle.siegeframe</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>공성 프레임</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E81" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F81" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G81" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
+      <x:c r="J81" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K81"/>
+      <x:c r="L81" t="str">
+        <x:v>중장갑 프레임과 대형 총열로 지속 화력을 견디는 군용 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M81" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N81" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O81" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>item.weapon.rifle.emberline</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>잔불 선로</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E82" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F82" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G82" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H82"/>
+      <x:c r="I82"/>
+      <x:c r="J82" t="str">
+        <x:v>Fire</x:v>
+      </x:c>
+      <x:c r="K82"/>
+      <x:c r="L82" t="str">
+        <x:v>주황색 에너지 셀을 직선으로 배열해 열 방출을 안정시킨 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M82" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N82" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O82" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>item.weapon.rifle.whitenoise</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>백색 소음</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E83" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F83" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G83" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H83"/>
+      <x:c r="I83"/>
+      <x:c r="J83" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K83"/>
+      <x:c r="L83" t="str">
+        <x:v>불필요한 장식을 줄인 백색 프레임의 장거리 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M83" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N83" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O83" t="n">
+        <x:v>600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>item.weapon.rifle.arcvector</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>아크 벡터</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E84" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F84" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G84" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H84"/>
+      <x:c r="I84"/>
+      <x:c r="J84" t="str">
+        <x:v>Electric</x:v>
+      </x:c>
+      <x:c r="K84" t="str">
+        <x:v>UE_ArcVector</x:v>
+      </x:c>
+      <x:c r="L84" t="str">
+        <x:v>청록 전류가 총열을 따라 정렬되도록 설계된 고속 에너지 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M84" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N84" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O84" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>item.weapon.rifle.bluehorizon</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>푸른 지평선</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E85" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F85" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G85" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H85"/>
+      <x:c r="I85"/>
+      <x:c r="J85" t="str">
+        <x:v>Electric</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>UE_BlueHorizon</x:v>
+      </x:c>
+      <x:c r="L85" t="str">
+        <x:v>푸른 에너지 노심과 정밀 조준계를 결합한 최상급 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M85" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O85" t="n">
+        <x:v>14000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>item.weapon.rifle.redsingularity</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>적색 특이점</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E86" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F86" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G86" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H86"/>
+      <x:c r="I86"/>
+      <x:c r="J86" t="str">
+        <x:v>Fire</x:v>
+      </x:c>
+      <x:c r="K86" t="str">
+        <x:v>UE_RedSingularity</x:v>
+      </x:c>
+      <x:c r="L86" t="str">
+        <x:v>적색 코일이 특이점 전하를 집속하는 실험형 중형 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M86" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N86" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O86" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R9fdc427c09634b4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R24ff8042327d4ccb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Raabc0a8f2da94690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R9c112b282a2044ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rad3d5126b6b14c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R21d746c5a3094c6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R9a5320f4897e4cc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R4daaa034c28541b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Rfb33918f85c44c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R5d657a1807344ce5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5102,6 +5102,508 @@
         <x:v>15000</x:v>
       </x:c>
     </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>item.weapon.shotgun.dockbreaker</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>부두의 철퇴</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E87" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F87" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G87" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H87"/>
+      <x:c r="I87"/>
+      <x:c r="J87" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K87"/>
+      <x:c r="L87" t="str">
+        <x:v>부두 계류 장비를 충격파 산탄총으로 개조했습니다. 닻을 닮은 넓은 총구가 반동을 붙잡습니다.</x:v>
+      </x:c>
+      <x:c r="M87" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N87" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O87" t="n">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>item.weapon.rifle.phaseorchid</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>허공에 핀 난초</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E88" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F88" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G88" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H88"/>
+      <x:c r="I88"/>
+      <x:c r="J88" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K88" t="str">
+        <x:v>UE_PhaseOrchid</x:v>
+      </x:c>
+      <x:c r="L88" t="str">
+        <x:v>다크 제이드 장갑 사이로 자홍빛 에너지가 피어나는 의전용 정밀 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M88" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N88" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O88" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>item.weapon.rifle.massproduced</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>양산형 라이플</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E89" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F89" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G89" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
+      <x:c r="J89" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K89"/>
+      <x:c r="L89" t="str">
+        <x:v>규격 부품으로 대량 생산된 표준형 에너지 라이플입니다. 화려하진 않지만 어디서나 같은 성능을 냅니다.</x:v>
+      </x:c>
+      <x:c r="M89" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N89" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O89" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>item.weapon.shotgun.homesafety</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>가정용 안전 용품</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E90" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F90" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H90"/>
+      <x:c r="I90"/>
+      <x:c r="J90" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K90"/>
+      <x:c r="L90" t="str">
+        <x:v>가정용 충격 억제 장치를 산탄총으로 개조했습니다. 비살상이라는 표시는 오래전에 지워졌습니다.</x:v>
+      </x:c>
+      <x:c r="M90" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N90" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O90" t="n">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>item.weapon.rifle.fieldmod</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>개조된 라이플</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F91" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H91"/>
+      <x:c r="I91"/>
+      <x:c r="J91" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K91"/>
+      <x:c r="L91" t="str">
+        <x:v>현장에서 주운 패널과 방열판을 덧대 성능을 끌어올린 개조형 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M91" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N91" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O91" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>item.weapon.rifle.outdoorhunter</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>아웃도어 헌팅 라이플</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>Rifle</x:v>
+      </x:c>
+      <x:c r="E92" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F92" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H92"/>
+      <x:c r="I92"/>
+      <x:c r="J92" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K92"/>
+      <x:c r="L92" t="str">
+        <x:v>목재 모방 소재와 에너지 총열을 결합한 장거리 사냥용 라이플입니다.</x:v>
+      </x:c>
+      <x:c r="M92" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N92" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O92" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>item.weapon.grenadelauncher.fireworks</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>폭죽놀이</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E93" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F93" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H93"/>
+      <x:c r="I93"/>
+      <x:c r="J93" t="str">
+        <x:v>Fire</x:v>
+      </x:c>
+      <x:c r="K93"/>
+      <x:c r="L93" t="str">
+        <x:v>다색 탄두를 차례로 점화해 전장을 축제처럼 밝히는 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O93" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>item.weapon.shotgun.sulbing</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>설빙</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>Rare</x:v>
+      </x:c>
+      <x:c r="F94" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H94"/>
+      <x:c r="I94"/>
+      <x:c r="J94" t="str">
+        <x:v>Ice</x:v>
+      </x:c>
+      <x:c r="K94"/>
+      <x:c r="L94" t="str">
+        <x:v>넓은 냉각 총구로 압축 냉기를 한꺼번에 방출하는 산탄총입니다.</x:v>
+      </x:c>
+      <x:c r="M94" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N94" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O94" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>item.weapon.grenadelauncher.glasscannon</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>유리대포</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F95" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H95"/>
+      <x:c r="I95"/>
+      <x:c r="J95" t="str">
+        <x:v>Electric</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>UE_GlassCannon</x:v>
+      </x:c>
+      <x:c r="L95" t="str">
+        <x:v>투명 덮개 안의 취약한 고출력 코어를 한계까지 밀어붙인 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M95" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O95" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>item.weapon.shotgun.incinerator</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>소각 산탄총</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="F96" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H96"/>
+      <x:c r="I96"/>
+      <x:c r="J96" t="str">
+        <x:v>Fire</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>UE_Incinerator</x:v>
+      </x:c>
+      <x:c r="L96" t="str">
+        <x:v>폐기물 소각로의 압력 챔버를 개조해 불길을 산탄처럼 쏟아내는 중화기입니다.</x:v>
+      </x:c>
+      <x:c r="M96" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N96" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O96" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>item.weapon.grenadelauncher.apocalypse</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>묵시록적 파괴</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H97"/>
+      <x:c r="I97"/>
+      <x:c r="J97" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>UE_Apocalypse</x:v>
+      </x:c>
+      <x:c r="L97" t="str">
+        <x:v>여러 개의 봉인 코어가 순차 붕괴하며 종말급 충격을 만드는 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O97" t="n">
+        <x:v>16000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>item.weapon.shotgun.conversationstarter</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>훌륭한 대화수단</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>Shotgun</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>Legendary</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
+      <x:c r="J98" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>UE_ConversationStarter</x:v>
+      </x:c>
+      <x:c r="L98" t="str">
+        <x:v>대화가 통하지 않을 때 꺼내는 거대한 일체형 충격파 산탄 장비입니다.</x:v>
+      </x:c>
+      <x:c r="M98" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N98" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O98" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R21d746c5a3094c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R9a5320f4897e4cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R4daaa034c28541b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Rfb33918f85c44c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R5d657a1807344ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="Rae7db427a84a470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Rbc7c8b0e701f4f08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rf1c14da0cde34156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Rf67b9677f4434524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R3dc721a167c14aec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5604,6 +5604,264 @@
         <x:v>15000</x:v>
       </x:c>
     </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>item.weapon.greatsword.carrotknife</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>당근칼</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Fighter</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>GreatSword</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H99"/>
+      <x:c r="I99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K99"/>
+      <x:c r="L99" t="str">
+        <x:v>장난감처럼 귀엽지만 양손으로 휘둘러야 하는 큼직한 당근 모양 대검입니다.</x:v>
+      </x:c>
+      <x:c r="M99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O99" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>item.weapon.grenadelauncher.shellcourier</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>탄두 배달부</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H100"/>
+      <x:c r="I100" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J100" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K100"/>
+      <x:c r="L100" t="str">
+        <x:v>공장 물류용 공압 실린더를 단발식 유탄발사기로 개조했습니다. 단순하지만 탄두는 정확히 배달합니다.</x:v>
+      </x:c>
+      <x:c r="M100" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N100" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O100" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>item.weapon.grenadelauncher.bouncebuddy</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>바운스 버디</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H101"/>
+      <x:c r="I101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K101"/>
+      <x:c r="L101" t="str">
+        <x:v>둥근 고무 완충통과 청록색 조준등을 단 소형 유탄발사기입니다. 통통 튀는 외형이 반동을 부드럽게 받아냅니다.</x:v>
+      </x:c>
+      <x:c r="M101" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N101" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O101" t="n">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>item.weapon.grenadelauncher.scraphopper</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>고철 호퍼</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H102"/>
+      <x:c r="I102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K102"/>
+      <x:c r="L102" t="str">
+        <x:v>폐기된 광물 호퍼와 작업장 배관을 이어 붙인 드럼식 유탄발사기입니다. 묵직한 골격이 발사 흔들림을 잡아줍니다.</x:v>
+      </x:c>
+      <x:c r="M102" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N102" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O102" t="n">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>item.weapon.grenadelauncher.clusterpop</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>클러스터 팝</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H103"/>
+      <x:c r="I103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K103"/>
+      <x:c r="L103" t="str">
+        <x:v>세 개의 소형 캡슐을 하나의 탄두로 묶어 발사 순서를 안정화한 고급 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M103" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N103" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O103" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>item.weapon.grenadelauncher.smartfuse</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>스마트 퓨즈</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H104"/>
+      <x:c r="I104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K104"/>
+      <x:c r="L104" t="str">
+        <x:v>비행 거리를 계산해 탄두의 기폭 시간을 조절하는 프로그래머블 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M104" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O104" t="n">
+        <x:v>700</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="Rae7db427a84a470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Rbc7c8b0e701f4f08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rf1c14da0cde34156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Rf67b9677f4434524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R3dc721a167c14aec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R50cb32390b7741ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R64c5b0d721444615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rf0fd444d0a36417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R24539ce8f81e4066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R7927e6d2d6a8457e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4145,7 +4145,7 @@
         <x:v>Rifle</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>Advanced</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F64" t="str">
         <x:v>attackPowerFlat</x:v>
@@ -4158,7 +4158,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>None</x:v>
+        <x:v>Ice</x:v>
       </x:c>
       <x:c r="K64"/>
       <x:c r="L64" t="str">
@@ -4244,7 +4244,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>None</x:v>
+        <x:v>Ice</x:v>
       </x:c>
       <x:c r="K66"/>
       <x:c r="L66" t="str">
@@ -4946,7 +4946,7 @@
         <x:v>Rifle</x:v>
       </x:c>
       <x:c r="E83" t="str">
-        <x:v>Advanced</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F83" t="str">
         <x:v>attackPowerFlat</x:v>
@@ -4957,7 +4957,7 @@
       <x:c r="H83"/>
       <x:c r="I83"/>
       <x:c r="J83" t="str">
-        <x:v>None</x:v>
+        <x:v>Ice</x:v>
       </x:c>
       <x:c r="K83"/>
       <x:c r="L83" t="str">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R21d746c5a3094c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R9a5320f4897e4cc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R4daaa034c28541b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Rfb33918f85c44c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R5d657a1807344ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R50cb32390b7741ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R64c5b0d721444615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rf0fd444d0a36417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R24539ce8f81e4066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R7927e6d2d6a8457e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4145,7 +4145,7 @@
         <x:v>Rifle</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>Advanced</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F64" t="str">
         <x:v>attackPowerFlat</x:v>
@@ -4158,7 +4158,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>None</x:v>
+        <x:v>Ice</x:v>
       </x:c>
       <x:c r="K64"/>
       <x:c r="L64" t="str">
@@ -4244,7 +4244,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>None</x:v>
+        <x:v>Ice</x:v>
       </x:c>
       <x:c r="K66"/>
       <x:c r="L66" t="str">
@@ -4946,7 +4946,7 @@
         <x:v>Rifle</x:v>
       </x:c>
       <x:c r="E83" t="str">
-        <x:v>Advanced</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="F83" t="str">
         <x:v>attackPowerFlat</x:v>
@@ -4957,7 +4957,7 @@
       <x:c r="H83"/>
       <x:c r="I83"/>
       <x:c r="J83" t="str">
-        <x:v>None</x:v>
+        <x:v>Ice</x:v>
       </x:c>
       <x:c r="K83"/>
       <x:c r="L83" t="str">
@@ -5602,6 +5602,264 @@
       </x:c>
       <x:c r="O98" t="n">
         <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>item.weapon.greatsword.carrotknife</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>당근칼</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Fighter</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>GreatSword</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H99"/>
+      <x:c r="I99" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K99"/>
+      <x:c r="L99" t="str">
+        <x:v>장난감처럼 귀엽지만 양손으로 휘둘러야 하는 큼직한 당근 모양 대검입니다.</x:v>
+      </x:c>
+      <x:c r="M99" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N99" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O99" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>item.weapon.grenadelauncher.shellcourier</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>탄두 배달부</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H100"/>
+      <x:c r="I100" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J100" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K100"/>
+      <x:c r="L100" t="str">
+        <x:v>공장 물류용 공압 실린더를 단발식 유탄발사기로 개조했습니다. 단순하지만 탄두는 정확히 배달합니다.</x:v>
+      </x:c>
+      <x:c r="M100" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N100" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O100" t="n">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>item.weapon.grenadelauncher.bouncebuddy</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>바운스 버디</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H101"/>
+      <x:c r="I101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K101"/>
+      <x:c r="L101" t="str">
+        <x:v>둥근 고무 완충통과 청록색 조준등을 단 소형 유탄발사기입니다. 통통 튀는 외형이 반동을 부드럽게 받아냅니다.</x:v>
+      </x:c>
+      <x:c r="M101" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N101" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O101" t="n">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>item.weapon.grenadelauncher.scraphopper</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>고철 호퍼</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>Common</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G102" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H102"/>
+      <x:c r="I102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K102"/>
+      <x:c r="L102" t="str">
+        <x:v>폐기된 광물 호퍼와 작업장 배관을 이어 붙인 드럼식 유탄발사기입니다. 묵직한 골격이 발사 흔들림을 잡아줍니다.</x:v>
+      </x:c>
+      <x:c r="M102" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N102" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O102" t="n">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>item.weapon.grenadelauncher.clusterpop</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>클러스터 팝</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G103" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H103"/>
+      <x:c r="I103" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K103"/>
+      <x:c r="L103" t="str">
+        <x:v>세 개의 소형 캡슐을 하나의 탄두로 묶어 발사 순서를 안정화한 고급 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M103" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N103" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O103" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>item.weapon.grenadelauncher.smartfuse</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>스마트 퓨즈</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Gunner</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>GrenadeLauncher</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>Advanced</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>attackPowerFlat</x:v>
+      </x:c>
+      <x:c r="G104" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H104"/>
+      <x:c r="I104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="K104"/>
+      <x:c r="L104" t="str">
+        <x:v>비행 거리를 계산해 탄두의 기폭 시간을 조절하는 프로그래머블 유탄발사기입니다.</x:v>
+      </x:c>
+      <x:c r="M104" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O104" t="n">
+        <x:v>700</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -4330,7 +4330,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>None</x:v>
+        <x:v>Fire</x:v>
       </x:c>
       <x:c r="K68"/>
       <x:c r="L68" t="str">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R50cb32390b7741ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R64c5b0d721444615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rf0fd444d0a36417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R24539ce8f81e4066"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R7927e6d2d6a8457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R033ca4ce1fd842af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R111b1be469e34ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rdd41903b203c4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R14b06fd1d2e749dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R1bf2b26a0c8c4d6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1982,6 +1982,9 @@
       <x:c r="J9" t="s">
         <x:v>31</x:v>
       </x:c>
+      <x:c r="K9" t="str">
+        <x:v>UE_InfernoExtraHit</x:v>
+      </x:c>
       <x:c r="L9" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -2709,6 +2712,9 @@
       </x:c>
       <x:c r="J28" s="11" t="s">
         <x:v>37</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>UE_ArcBladeChainLightning</x:v>
       </x:c>
       <x:c r="L28" s="11" t="s">
         <x:v>114</x:v>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R033ca4ce1fd842af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R111b1be469e34ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Rdd41903b203c4fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R14b06fd1d2e749dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R1bf2b26a0c8c4d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R5896b331624248b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R0a1f65daa1f14ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R4ac6b696193d4e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R1798e6f18ad44efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R1ff6feab87bd407f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4166,7 +4166,9 @@
       <x:c r="J64" t="str">
         <x:v>Ice</x:v>
       </x:c>
-      <x:c r="K64"/>
+      <x:c r="K64" t="str">
+        <x:v>UE_GlassRailExtraHit</x:v>
+      </x:c>
       <x:c r="L64" t="str">
         <x:v>투명 덮개 속 단일 에너지 도관을 사용하는 정밀 라이플입니다.</x:v>
       </x:c>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -6621,6 +6621,11 @@
       <c r="N7">
         <v>1000</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
@@ -8230,7 +8235,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -8705,6 +8710,47 @@
       </c>
       <c r="I16">
         <v>4500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.relic.manarelay</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마나 중계기</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주변 동료에게 회복 에너지를 전달하는 휴대용 중계 장치입니다.</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2195,9 +2195,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O104"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" ns3:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="35.5" customWidth="1"/>
     <col min="2" max="3" width="18.296875" customWidth="1"/>
@@ -2215,7 +2215,7 @@
     <col min="15" max="15" width="8.796875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" s="10" customFormat="1" ns3:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" s="10" customFormat="1" ns3:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" ns3:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ns3:dyDescent="0.4">
       <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" ns3:dyDescent="0.4">
       <c r="A5" s="11" t="s">
         <v>33</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" ns3:dyDescent="0.4">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" ns3:dyDescent="0.4">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" ns3:dyDescent="0.4">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" ns3:dyDescent="0.4">
       <c r="A9" t="s">
         <v>52</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" ns3:dyDescent="0.4">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" ns3:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" ns3:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>62</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" ns3:dyDescent="0.4">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" ns3:dyDescent="0.4">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" ns3:dyDescent="0.4">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" ns3:dyDescent="0.4">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" ns3:dyDescent="0.4">
       <c r="A17" t="s">
         <v>78</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" ns3:dyDescent="0.4">
       <c r="A18" s="11" t="s">
         <v>81</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ns3:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>85</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ns3:dyDescent="0.4">
       <c r="A20" s="11" t="s">
         <v>88</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" ns3:dyDescent="0.4">
       <c r="A21" s="11" t="s">
         <v>91</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" ns3:dyDescent="0.4">
       <c r="A22" s="11" t="s">
         <v>94</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" ns3:dyDescent="0.4">
       <c r="A23" s="11" t="s">
         <v>97</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" ns3:dyDescent="0.4">
       <c r="A24" s="11" t="s">
         <v>100</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" ns3:dyDescent="0.4">
       <c r="A25" s="11" t="s">
         <v>103</v>
       </c>
@@ -3182,6 +3182,11 @@
       <c r="J25" s="11" t="s">
         <v>24</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>UE_NightSwordDodgeStrike</t>
+        </is>
+      </c>
       <c r="L25" s="12" t="s">
         <v>105</v>
       </c>
@@ -3195,7 +3200,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" ns3:dyDescent="0.4">
       <c r="A26" s="11" t="s">
         <v>106</v>
       </c>
@@ -3233,7 +3238,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:15" ns3:dyDescent="0.4">
       <c r="A27" s="11" t="s">
         <v>109</v>
       </c>
@@ -3271,7 +3276,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:15" ns3:dyDescent="0.4">
       <c r="A28" s="11" t="s">
         <v>112</v>
       </c>
@@ -3312,7 +3317,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:15" ns3:dyDescent="0.4">
       <c r="A29" s="11" t="s">
         <v>115</v>
       </c>
@@ -3350,7 +3355,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" ns3:dyDescent="0.4">
       <c r="A30" s="11" t="s">
         <v>118</v>
       </c>
@@ -3388,7 +3393,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" ns3:dyDescent="0.4">
       <c r="A31" s="11" t="s">
         <v>121</v>
       </c>
@@ -3426,7 +3431,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" ns3:dyDescent="0.4">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -3464,7 +3469,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:15" ns3:dyDescent="0.4">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -3502,7 +3507,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:15" ns3:dyDescent="0.4">
       <c r="A34" t="s">
         <v>130</v>
       </c>
@@ -3540,7 +3545,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:15" ns3:dyDescent="0.4">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -3578,7 +3583,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:15" ns3:dyDescent="0.4">
       <c r="A36" t="s">
         <v>136</v>
       </c>
@@ -3619,7 +3624,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" ns3:dyDescent="0.4">
       <c r="A37" t="s">
         <v>140</v>
       </c>
@@ -3660,7 +3665,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:15" ns3:dyDescent="0.4">
       <c r="A38" t="s">
         <v>144</v>
       </c>
@@ -3698,7 +3703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:15" ns3:dyDescent="0.4">
       <c r="A39" t="s">
         <v>147</v>
       </c>
@@ -3736,7 +3741,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:15" ns3:dyDescent="0.4">
       <c r="A40" t="s">
         <v>150</v>
       </c>
@@ -3774,7 +3779,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:15" ns3:dyDescent="0.4">
       <c r="A41" t="s">
         <v>153</v>
       </c>
@@ -3812,7 +3817,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:15" ns3:dyDescent="0.4">
       <c r="A42" t="s">
         <v>156</v>
       </c>
@@ -3853,7 +3858,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:15" ns3:dyDescent="0.4">
       <c r="A43" t="s">
         <v>160</v>
       </c>
@@ -3894,7 +3899,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:15" ns3:dyDescent="0.4">
       <c r="A44" t="s">
         <v>164</v>
       </c>
@@ -3932,7 +3937,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" ns3:dyDescent="0.4">
       <c r="A45" t="s">
         <v>167</v>
       </c>
@@ -3970,7 +3975,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:15" ns3:dyDescent="0.4">
       <c r="A46" t="s">
         <v>170</v>
       </c>
@@ -4008,7 +4013,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:15" ns3:dyDescent="0.4">
       <c r="A47" t="s">
         <v>173</v>
       </c>
@@ -4046,7 +4051,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:15" ns3:dyDescent="0.4">
       <c r="A48" t="s">
         <v>176</v>
       </c>
@@ -4087,7 +4092,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" ns3:dyDescent="0.4">
       <c r="A49" t="s">
         <v>180</v>
       </c>
@@ -4128,7 +4133,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:15" ns3:dyDescent="0.4">
       <c r="A50" t="s">
         <v>184</v>
       </c>
@@ -4166,7 +4171,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:15" ns3:dyDescent="0.4">
       <c r="A51" s="11" t="s">
         <v>187</v>
       </c>
@@ -4204,7 +4209,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:15" ns3:dyDescent="0.4">
       <c r="A52" t="s">
         <v>432</v>
       </c>
@@ -4245,7 +4250,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:15" ns3:dyDescent="0.4">
       <c r="A53" t="s">
         <v>435</v>
       </c>
@@ -4286,7 +4291,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:15" ns3:dyDescent="0.4">
       <c r="A54" t="s">
         <v>438</v>
       </c>
@@ -4327,7 +4332,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:15" ns3:dyDescent="0.4">
       <c r="A55" t="s">
         <v>441</v>
       </c>
@@ -4368,7 +4373,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:15" ns3:dyDescent="0.4">
       <c r="A56" t="s">
         <v>444</v>
       </c>
@@ -4409,7 +4414,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:15" ns3:dyDescent="0.4">
       <c r="A57" t="s">
         <v>447</v>
       </c>
@@ -4450,7 +4455,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:15" ns3:dyDescent="0.4">
       <c r="A58" t="s">
         <v>450</v>
       </c>
@@ -4491,7 +4496,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:15" ns3:dyDescent="0.4">
       <c r="A59" t="s">
         <v>453</v>
       </c>
@@ -4532,7 +4537,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:15" ns3:dyDescent="0.4">
       <c r="A60" t="s">
         <v>456</v>
       </c>
@@ -4573,7 +4578,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:15" ns3:dyDescent="0.4">
       <c r="A61" t="s">
         <v>459</v>
       </c>
@@ -4614,7 +4619,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:15" ns3:dyDescent="0.4">
       <c r="A62" t="s">
         <v>462</v>
       </c>
@@ -4655,7 +4660,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:15" ns3:dyDescent="0.4">
       <c r="A63" t="s">
         <v>465</v>
       </c>
@@ -4696,7 +4701,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:15" ns3:dyDescent="0.4">
       <c r="A64" t="s">
         <v>468</v>
       </c>
@@ -4740,7 +4745,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:15" ns3:dyDescent="0.4">
       <c r="A65" t="s">
         <v>472</v>
       </c>
@@ -4781,7 +4786,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:15" ns3:dyDescent="0.4">
       <c r="A66" t="s">
         <v>475</v>
       </c>
@@ -4822,7 +4827,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:15" ns3:dyDescent="0.4">
       <c r="A67" t="s">
         <v>478</v>
       </c>
@@ -4863,7 +4868,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:15" ns3:dyDescent="0.4">
       <c r="A68" t="s">
         <v>481</v>
       </c>
@@ -4904,7 +4909,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:15" ns3:dyDescent="0.4">
       <c r="A69" t="s">
         <v>484</v>
       </c>
@@ -4945,7 +4950,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:15" ns3:dyDescent="0.4">
       <c r="A70" t="s">
         <v>487</v>
       </c>
@@ -4986,7 +4991,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:15" ns3:dyDescent="0.4">
       <c r="A71" t="s">
         <v>491</v>
       </c>
@@ -5024,7 +5029,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:15" ns3:dyDescent="0.4">
       <c r="A72" t="s">
         <v>494</v>
       </c>
@@ -5065,7 +5070,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:15" ns3:dyDescent="0.4">
       <c r="A73" t="s">
         <v>498</v>
       </c>
@@ -5106,7 +5111,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:15" ns3:dyDescent="0.4">
       <c r="A74" t="s">
         <v>502</v>
       </c>
@@ -5144,7 +5149,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:15" ns3:dyDescent="0.4">
       <c r="A75" t="s">
         <v>505</v>
       </c>
@@ -5185,7 +5190,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:15" ns3:dyDescent="0.4">
       <c r="A76" t="s">
         <v>509</v>
       </c>
@@ -5223,7 +5228,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:15" ns3:dyDescent="0.4">
       <c r="A77" t="s">
         <v>512</v>
       </c>
@@ -5264,7 +5269,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:15" ns3:dyDescent="0.4">
       <c r="A78" t="s">
         <v>516</v>
       </c>
@@ -5302,7 +5307,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:15" ns3:dyDescent="0.4">
       <c r="A79" t="s">
         <v>519</v>
       </c>
@@ -5340,7 +5345,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:15" ns3:dyDescent="0.4">
       <c r="A80" t="s">
         <v>522</v>
       </c>
@@ -5378,7 +5383,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:15" ns3:dyDescent="0.4">
       <c r="A81" t="s">
         <v>525</v>
       </c>
@@ -5416,7 +5421,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:15" ns3:dyDescent="0.4">
       <c r="A82" t="s">
         <v>528</v>
       </c>
@@ -5454,7 +5459,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:15" ns3:dyDescent="0.4">
       <c r="A83" t="s">
         <v>531</v>
       </c>
@@ -5492,7 +5497,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:15" ns3:dyDescent="0.4">
       <c r="A84" t="s">
         <v>534</v>
       </c>
@@ -5533,7 +5538,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:15" ns3:dyDescent="0.4">
       <c r="A85" t="s">
         <v>538</v>
       </c>
@@ -5574,7 +5579,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:15" ns3:dyDescent="0.4">
       <c r="A86" t="s">
         <v>542</v>
       </c>
@@ -5615,7 +5620,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:15" ns3:dyDescent="0.4">
       <c r="A87" t="s">
         <v>546</v>
       </c>
@@ -5653,7 +5658,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:15" ns3:dyDescent="0.4">
       <c r="A88" t="s">
         <v>549</v>
       </c>
@@ -5694,7 +5699,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:15" ns3:dyDescent="0.4">
       <c r="A89" t="s">
         <v>553</v>
       </c>
@@ -5732,7 +5737,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:15" ns3:dyDescent="0.4">
       <c r="A90" t="s">
         <v>556</v>
       </c>
@@ -5770,7 +5775,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:15" ns3:dyDescent="0.4">
       <c r="A91" t="s">
         <v>559</v>
       </c>
@@ -5808,7 +5813,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:15" ns3:dyDescent="0.4">
       <c r="A92" t="s">
         <v>562</v>
       </c>
@@ -5846,7 +5851,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:15" ns3:dyDescent="0.4">
       <c r="A93" t="s">
         <v>565</v>
       </c>
@@ -5884,7 +5889,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:15" ns3:dyDescent="0.4">
       <c r="A94" t="s">
         <v>568</v>
       </c>
@@ -5922,7 +5927,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:15" ns3:dyDescent="0.4">
       <c r="A95" t="s">
         <v>571</v>
       </c>
@@ -5963,7 +5968,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:15" ns3:dyDescent="0.4">
       <c r="A96" t="s">
         <v>575</v>
       </c>
@@ -6004,7 +6009,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:15" ns3:dyDescent="0.4">
       <c r="A97" t="s">
         <v>579</v>
       </c>
@@ -6045,7 +6050,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:15" ns3:dyDescent="0.4">
       <c r="A98" t="s">
         <v>583</v>
       </c>
@@ -6086,7 +6091,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:15" ns3:dyDescent="0.4">
       <c r="A99" t="s">
         <v>587</v>
       </c>
@@ -6127,7 +6132,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:15" ns3:dyDescent="0.4">
       <c r="A100" t="s">
         <v>590</v>
       </c>
@@ -6168,7 +6173,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:15" ns3:dyDescent="0.4">
       <c r="A101" t="s">
         <v>593</v>
       </c>
@@ -6209,7 +6214,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:15" ns3:dyDescent="0.4">
       <c r="A102" t="s">
         <v>596</v>
       </c>
@@ -6250,7 +6255,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:15" ns3:dyDescent="0.4">
       <c r="A103" t="s">
         <v>599</v>
       </c>
@@ -6291,7 +6296,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:15" ns3:dyDescent="0.4">
       <c r="A104" t="s">
         <v>602</v>
       </c>
@@ -6684,6 +6689,11 @@
       <c r="G9">
         <v>80</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UE_SolarGraceShield</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="s">
         <v>221</v>
       </c>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="Re0a8cd3e0bb84f6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R39d2b6be06924279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R8d61f58fa3fa4a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R501e9281ab304177"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R43cdbccea8124d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R1556fa2538134961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Rb9fde9a8f2c04d92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R58746c4f75ab41a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R9debe87460d444f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rb12359b5737f4b08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4522,6 +4522,9 @@
       <x:c r="J60" t="s">
         <x:v>24</x:v>
       </x:c>
+      <x:c r="K60" t="str">
+        <x:v>UE_SingularityDelayedExplosion</x:v>
+      </x:c>
       <x:c r="L60" t="s">
         <x:v>220</x:v>
       </x:c>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="R1556fa2538134961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="Rb9fde9a8f2c04d92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="R58746c4f75ab41a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="R9debe87460d444f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="Rb12359b5737f4b08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WeaponDefinitions" sheetId="1" r:id="Rc16d7b70afcb4413"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ArmorDefinitions" sheetId="2" r:id="R77ff1f4ad6d84686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PotionDefinitions" sheetId="3" r:id="Re4ee5132b0854e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelicDefinitions" sheetId="4" r:id="Rc0a53bd06c1944f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="5" r:id="R13a1c28eaa5b49eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -218,118 +218,118 @@
     <x:t xml:space="preserve">수호자의 정의</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">정의는 승리한다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.blunt.ironpipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">쇠 파이프</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">고철 처리장에서 가져온 녹 슨 파이프입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.greatsword.zeroblade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">제로 블레이드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">절대영도에 가까운 냉각장을 방출합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.greatsword.solarblade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">솔라 블레이드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">태양의 핵융합을 모방한 플라즈마 칼날.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.greatsword.voltblade</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">볼트 블레이드</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">수백만 볼트의 전위를 한 줄기로 압축했습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.axe.heartofdebris</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">데브리스 심장 도끼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UE_HeartOfDebris</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">데브리스-9의 결정체가 응축된 전설 무기입니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.greatsword.wasteheatcleaver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">폐열 절단 대검</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">거대한 칼날은 폐열을 가장자리에 집중시켜 견고한 기계도 절단할 수 있게 해줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.axe.wildfire</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">와일드파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">꺼지지 않는 불씨를 품은 도끼입니다. 휘두를 때마다 잠들어 있던 열기가 다시 타오릅니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.blunt.thighbone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">우주 괴물 대퇴골</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">정체불명의 우주 괴물에게서 나온 대퇴골입니다. 뼈라고 믿기 어려울 만큼 무겁고 단단합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.blunt.superrefrigerant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">초냉매</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">극저온의 냉매가 봉인되어 있습니다. 충격을 받을 때마다 주변의 열을 무자비하게 빼앗습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.blunt.morningstar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">아침의 별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">새벽하늘에서 가장 밝게 빛나는 별의 이름을 가진 무기입니다. 맞은 사람도 잠시 별을 볼 수 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.blunt.magicstaff</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">마법(물리) 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">마력이 없어도 사용할 수 있는 마법 지팡이입니다. 주문은 간단합니다. 힘껏 휘두르세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">item.weapon.greatsword.nightsword</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">밤의 칼날</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Unique</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">정의는 승리한다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.blunt.ironpipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">쇠 파이프</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">고철 처리장에서 가져온 녹 슨 파이프입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.greatsword.zeroblade</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">제로 블레이드</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">절대영도에 가까운 냉각장을 방출합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.greatsword.solarblade</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">솔라 블레이드</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">태양의 핵융합을 모방한 플라즈마 칼날.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.greatsword.voltblade</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">볼트 블레이드</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">수백만 볼트의 전위를 한 줄기로 압축했습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.axe.heartofdebris</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">데브리스 심장 도끼</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UE_HeartOfDebris</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">데브리스-9의 결정체가 응축된 전설 무기입니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.greatsword.wasteheatcleaver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">폐열 절단 대검</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">거대한 칼날은 폐열을 가장자리에 집중시켜 견고한 기계도 절단할 수 있게 해줍니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.axe.wildfire</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">와일드파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">꺼지지 않는 불씨를 품은 도끼입니다. 휘두를 때마다 잠들어 있던 열기가 다시 타오릅니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.blunt.thighbone</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">우주 괴물 대퇴골</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">정체불명의 우주 괴물에게서 나온 대퇴골입니다. 뼈라고 믿기 어려울 만큼 무겁고 단단합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.blunt.superrefrigerant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">초냉매</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">극저온의 냉매가 봉인되어 있습니다. 충격을 받을 때마다 주변의 열을 무자비하게 빼앗습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.blunt.morningstar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">아침의 별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">새벽하늘에서 가장 밝게 빛나는 별의 이름을 가진 무기입니다. 맞은 사람도 잠시 별을 볼 수 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.blunt.magicstaff</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">마법(물리) 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">마력이 없어도 사용할 수 있는 마법 지팡이입니다. 주문은 간단합니다. 힘껏 휘두르세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">item.weapon.greatsword.nightsword</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">밤의 칼날</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">빛을 삼킨 듯 검게 물든 대검입니다. 어둠 속에서는 칼날의 경계조차 흐릿해집니다.</x:t>
@@ -2665,8 +2665,8 @@
       <x:c r="D13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E13" t="s">
-        <x:v>68</x:v>
+      <x:c r="E13" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F13" t="s">
         <x:v>23</x:v>
@@ -2678,7 +2678,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L13" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="M13" s="8">
         <x:v>1</x:v>
@@ -2692,10 +2692,10 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B14" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="C14" t="s">
         <x:v>20</x:v>
@@ -2716,7 +2716,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L14" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M14" s="8">
         <x:v>1</x:v>
@@ -2730,10 +2730,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B15" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="B15" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="C15" t="s">
         <x:v>20</x:v>
@@ -2754,7 +2754,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L15" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="M15">
         <x:v>1</x:v>
@@ -2768,10 +2768,10 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B16" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="C16" t="s">
         <x:v>20</x:v>
@@ -2792,7 +2792,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L16" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="M16">
         <x:v>1</x:v>
@@ -2806,10 +2806,10 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B17" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="C17" t="s">
         <x:v>20</x:v>
@@ -2830,7 +2830,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L17" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="M17">
         <x:v>1</x:v>
@@ -2844,10 +2844,10 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B18" s="11" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="C18" s="11" t="s">
         <x:v>20</x:v>
@@ -2868,10 +2868,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="K18" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="M18" s="8">
         <x:v>2</x:v>
@@ -2885,10 +2885,10 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B19" s="11" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B19" s="11" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C19" s="11" t="s">
         <x:v>20</x:v>
@@ -2896,8 +2896,8 @@
       <x:c r="D19" s="11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="s">
-        <x:v>68</x:v>
+      <x:c r="E19" s="11" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F19" s="11" t="s">
         <x:v>23</x:v>
@@ -2909,7 +2909,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L19" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="M19" s="8">
         <x:v>2</x:v>
@@ -2923,10 +2923,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B20" s="11" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="B20" s="11" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="11" t="s">
         <x:v>20</x:v>
@@ -2934,8 +2934,8 @@
       <x:c r="D20" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
-        <x:v>68</x:v>
+      <x:c r="E20" s="11" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F20" s="11" t="s">
         <x:v>23</x:v>
@@ -2947,7 +2947,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="L20" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="M20" s="8">
         <x:v>2</x:v>
@@ -2961,10 +2961,10 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B21" s="11" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B21" s="11" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="C21" s="11" t="s">
         <x:v>20</x:v>
@@ -2985,7 +2985,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L21" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="M21" s="8">
         <x:v>2</x:v>
@@ -2999,10 +2999,10 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B22" s="11" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="B22" s="11" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="C22" s="11" t="s">
         <x:v>20</x:v>
@@ -3010,8 +3010,8 @@
       <x:c r="D22" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E22" s="11" t="s">
-        <x:v>68</x:v>
+      <x:c r="E22" s="11" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F22" s="11" t="s">
         <x:v>23</x:v>
@@ -3023,7 +3023,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L22" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="M22" s="8">
         <x:v>2</x:v>
@@ -3037,10 +3037,10 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B23" s="11" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B23" s="11" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="C23" s="11" t="s">
         <x:v>20</x:v>
@@ -3061,7 +3061,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="L23" s="12" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="M23" s="8">
         <x:v>1</x:v>
@@ -3075,10 +3075,10 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B24" s="11" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B24" s="11" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="C24" s="11" t="s">
         <x:v>20</x:v>
@@ -3099,7 +3099,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="M24" s="8">
         <x:v>1</x:v>
@@ -3113,10 +3113,10 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B25" s="11" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B25" s="11" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="C25" s="11" t="s">
         <x:v>20</x:v>
@@ -3125,7 +3125,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E25" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F25" s="11" t="s">
         <x:v>23</x:v>
@@ -3243,8 +3243,8 @@
       <x:c r="D28" s="11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E28" s="11" t="s">
-        <x:v>68</x:v>
+      <x:c r="E28" s="11" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F28" s="11" t="s">
         <x:v>23</x:v>
@@ -3284,8 +3284,8 @@
       <x:c r="D29" s="11" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E29" s="11" t="s">
-        <x:v>68</x:v>
+      <x:c r="E29" s="11" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F29" s="11" t="s">
         <x:v>23</x:v>
@@ -3551,7 +3551,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F36" t="s">
         <x:v>23</x:v>
@@ -3785,7 +3785,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="E42" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F42" t="s">
         <x:v>23</x:v>
@@ -4019,7 +4019,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E48" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F48" t="s">
         <x:v>23</x:v>
@@ -4381,8 +4381,8 @@
       <x:c r="D57" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="E57" t="s">
-        <x:v>68</x:v>
+      <x:c r="E57" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F57" t="s">
         <x:v>23</x:v>
@@ -4425,8 +4425,8 @@
       <x:c r="D58" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="E58" t="s">
-        <x:v>68</x:v>
+      <x:c r="E58" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F58" t="s">
         <x:v>23</x:v>
@@ -4551,8 +4551,8 @@
       <x:c r="D61" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="E61" t="s">
-        <x:v>68</x:v>
+      <x:c r="E61" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F61" t="s">
         <x:v>23</x:v>
@@ -4800,8 +4800,8 @@
       <x:c r="D67" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E67" t="s">
-        <x:v>68</x:v>
+      <x:c r="E67" t="str">
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="F67" t="s">
         <x:v>23</x:v>
@@ -5003,7 +5003,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E72" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F72" t="s">
         <x:v>23</x:v>
@@ -5123,7 +5123,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E75" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F75" t="s">
         <x:v>23</x:v>
@@ -5202,7 +5202,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E77" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F77" t="s">
         <x:v>23</x:v>
@@ -5471,7 +5471,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E84" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F84" t="s">
         <x:v>23</x:v>
@@ -5632,7 +5632,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="E88" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F88" t="s">
         <x:v>23</x:v>
@@ -5901,7 +5901,7 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="E95" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F95" t="s">
         <x:v>23</x:v>
@@ -5942,7 +5942,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E96" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F96" t="s">
         <x:v>23</x:v>
@@ -6491,7 +6491,7 @@
         <x:v>382</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F5" t="s">
         <x:v>383</x:v>
@@ -7169,7 +7169,7 @@
         <x:v>373</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F24" t="s">
         <x:v>374</x:v>
@@ -7458,7 +7458,7 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F32" t="s">
         <x:v>378</x:v>
@@ -7747,7 +7747,7 @@
         <x:v>382</x:v>
       </x:c>
       <x:c r="E40" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F40" t="s">
         <x:v>383</x:v>
@@ -8397,7 +8397,7 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E7" s="11" t="s">
         <x:v>554</x:v>
@@ -8542,7 +8542,7 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E12" t="s">
         <x:v>574</x:v>
@@ -8571,7 +8571,7 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E13" t="s">
         <x:v>578</x:v>
@@ -8658,7 +8658,7 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E16" t="s">
         <x:v>590</x:v>
@@ -8822,7 +8822,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>68</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B5" t="s">
         <x:v>24</x:v>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -5563,8 +5563,13 @@
       <c r="G90" t="n">
         <v>48</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5625,8 +5630,13 @@
       <c r="G91" t="n">
         <v>66</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5687,8 +5697,13 @@
       <c r="G92" t="n">
         <v>66</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5749,8 +5764,13 @@
       <c r="G93" t="n">
         <v>66</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5811,6 +5831,14 @@
       <c r="G94" t="n">
         <v>76</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>-45</v>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>None</t>
@@ -5870,6 +5898,14 @@
       <c r="G95" t="n">
         <v>52</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>-45</v>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>Electric</t>
@@ -5929,6 +5965,14 @@
       <c r="G96" t="n">
         <v>30</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>-45</v>
+      </c>
       <c r="J96" s="13" t="inlineStr">
         <is>
           <t>Ice</t>
@@ -5988,8 +6032,13 @@
       <c r="G97" t="n">
         <v>30</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6045,6 +6094,14 @@
       <c r="G98" t="n">
         <v>35</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>-45</v>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>Fire</t>
@@ -6104,8 +6161,13 @@
       <c r="G99" t="n">
         <v>24</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6161,8 +6223,13 @@
       <c r="G100" t="n">
         <v>24</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6218,8 +6285,13 @@
       <c r="G101" t="n">
         <v>27</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6275,8 +6347,13 @@
       <c r="G102" t="n">
         <v>12</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -6332,8 +6409,13 @@
       <c r="G103" t="n">
         <v>15</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -6389,8 +6471,13 @@
       <c r="G104" t="n">
         <v>18</v>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -8904,13 +8991,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="16" t="n"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -2845,7 +2845,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="43">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
           <t>item.weapon.axe.phaseharvester</t>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>UE_PhaseHarvester</t>
+          <t>UE_PhaseHarvesterWave</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -4606,10 +4606,8 @@
           <t>None</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>UE_StarforgeBreach</t>
-        </is>
+      <c r="K73" t="str">
+        <v>UE_StarforgeBreachExplosion</v>
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -734,10 +734,8 @@
           <t>Fire</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>UE_WasteHeatCleaver</t>
-        </is>
+      <c r="K5" t="str" s="0">
+        <v>UE_WasteHeatDischarge</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>UE_Crusader</t>
+          <t>UE_CrusaderCriticalChain</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>UE_GuardiansJustice</t>
+          <t>UE_GuardiansJusticeShield</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>UE_CoreBreaker</t>
+          <t>UE_CoreBreakerArmorBreak</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>UE_SuperRefrigerant</t>
+          <t>UE_SuperRefrigerantFreeze</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>UE_Wildfire</t>
+          <t>UE_WildfireSpread</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>UE_AntimatterLance</t>
+          <t>UE_AntimatterPiercingShot</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>UE_SmileSignal</t>
+          <t>UE_SmileSignalMark</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>UE_EchoVault</t>
+          <t>UE_EchoVaultReplay</t>
         </is>
       </c>
       <c r="L72" s="14" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>UE_WorldEnder</t>
+          <t>UE_WorldEnderChargedBlast</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>UE_SunfallEngine</t>
+          <t>UE_SunfallBurnField</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UE_NinjaMovement</t>
+          <t>UE_NinjaDodgeAttack</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -734,8 +734,10 @@
           <t>Fire</t>
         </is>
       </c>
-      <c r="K5" t="str" s="0">
-        <v>UE_WasteHeatDischarge</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>UE_WasteHeatDischarge</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1366,6 +1368,11 @@
           <t>Electric</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>UE_RailSweep</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>자기 레일이 칼날을 따라 방전을 밀어내며 절단력을 높입니다.</t>
@@ -2106,6 +2113,11 @@
           <t>Fire</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>UE_PileDriverQuake</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>유압 실린더가 타격 순간 철심을 밀어내는 해체 공구입니다.</t>
@@ -2843,7 +2855,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="43">
+    <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
           <t>item.weapon.axe.phaseharvester</t>
@@ -3059,6 +3071,11 @@
           <t>Ice</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>UE_IceRush</t>
+        </is>
+      </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
           <t>강력한 냉기를 품은 도끼입니다.</t>
@@ -3761,6 +3778,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>UE_NovaCapacitor</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>코어 에너지를 길게 집중시키는 정밀 라이플입니다.</t>
@@ -4604,8 +4626,10 @@
           <t>None</t>
         </is>
       </c>
-      <c r="K73" t="str">
-        <v>UE_StarforgeBreachExplosion</v>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>UE_StarforgeBreachExplosion</t>
+        </is>
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>
@@ -5126,6 +5150,11 @@
           <t>Ice</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>UE_RecoilStep</t>
+        </is>
+      </c>
       <c r="L82" s="13" t="inlineStr">
         <is>
           <t>백색 외장과 냉각 앰풀로 반동열을 제어하는 경량 산탄총입니다.</t>
@@ -6039,6 +6068,11 @@
       <c r="J97" t="inlineStr">
         <is>
           <t>Ice</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>UE_HaloShrapnel</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6512,7 +6546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="38.3984375" customWidth="1" style="11" min="1" max="1"/>
@@ -8773,6 +8807,168 @@
       </c>
       <c r="N43" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.adrenalineinjector</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>아드레날린 주입기</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>healthFlat</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>150</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>UE_AdrenalineInjector</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>전투 신호를 받으면 정량보다 조금 많이 주입합니다. 조금만.</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>item.armor.helmet.heatexchanger</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>열교환 헬멧</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>healthFlat</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>160</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>UE_HeatExchanger</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>머리 위에서 열과 냉기, 전류를 순환시켜 스킬 회로를 안정시킵니다.</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>item.armor.chest.coolantarmor</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>냉각수 순환 갑주</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>defensePowerFlat</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>70</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>UE_CoolantArmor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>스킬의 반동열을 냉각수 관으로 흘려보내며 그 흐름으로 마나를 끌어올립니다.</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>12000</v>
       </c>
     </row>
   </sheetData>
@@ -9224,7 +9420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="27.59765625" customWidth="1" style="11" min="1" max="1"/>
@@ -9985,6 +10181,293 @@
       </c>
       <c r="I18" t="n">
         <v>2500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>item.relic.dampingcore</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>진동 감쇠 코어</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UE_DampingCore</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>지면 충격을 흡수해 스킬 출력으로 되돌리는 코어입니다. 대신 마나 순환이 둔해집니다.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>item.relic.overloadheart</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>과부하 심장</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UE_OverloadHeart</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>쓰러뜨린 기계의 잔류 전력을 빨아들여 각성 회로를 강제로 다시 돌립니다.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>item.relic.chargecircuit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>충전 회로</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UE_ChargeCircuit</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>처치 순간의 전류를 다음 사격용 축전지로 곧장 보내는 우회 회로입니다.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>item.relic.targetlens</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>표적 분석 렌즈</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UE_TargetLens</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>표식이 남긴 신호를 읽어 장갑의 이음매를 짚어 주는 조준 렌즈입니다.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>item.relic.manaconverter</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>마나 변환기</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>UE_ManaConverter</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>스킬을 쓰고 남은 마나 파동을 무기 출력으로 바꿔 줍니다.</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>item.relic.sparebattery</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>보조 배터리</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UE_SpareBattery</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>어디서 주웠는지 모를 휴대용 배터리입니다. 아직 눈금이 가득합니다.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>item.relic.elementresonator</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>원소 공명기</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Relic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UE_ElementResonator</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>서로 다른 원소가 한 점에서 겹치면 그 자리를 터뜨리는 불안정한 공명 장치입니다.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15000</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDataTable.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="8">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15">
@@ -1493,7 +1493,7 @@
         <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="24">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27">
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>3</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="41">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="43">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         <v>2</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="52">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>2</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="53">
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="60">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="63">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
         <v>2</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="73">
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>2</v>
       </c>
       <c r="O80" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="81">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>2</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="91">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="31">
